--- a/Results/Study 1/VGG11 (pretrained)/Confusion Matrices.xlsx
+++ b/Results/Study 1/VGG11 (pretrained)/Confusion Matrices.xlsx
@@ -400,10 +400,10 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="C2">
-        <v>179</v>
+        <v>176</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -411,10 +411,10 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>154</v>
+        <v>77</v>
       </c>
       <c r="C3">
-        <v>486</v>
+        <v>563</v>
       </c>
     </row>
   </sheetData>
@@ -440,10 +440,10 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C2">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -451,10 +451,10 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="C3">
-        <v>97</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>
